--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_13.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_13.xlsx
@@ -471,16 +471,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13918</v>
+        <v>50349</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luna da Rocha</t>
+          <t>Luana da Cunha</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -489,56 +489,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45088</v>
+        <v>45093</v>
       </c>
       <c r="G2" t="n">
-        <v>9619.549999999999</v>
+        <v>4641.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>34866</v>
+        <v>98657</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yasmin Rocha</t>
+          <t>Mariana Nascimento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45087</v>
+        <v>45092</v>
       </c>
       <c r="G3" t="n">
-        <v>6764.73</v>
+        <v>12207.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70364</v>
+        <v>41872</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vitor Hugo Cardoso</t>
+          <t>Helena Ferreira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45088</v>
+        <v>45096</v>
       </c>
       <c r="G4" t="n">
-        <v>11341.66</v>
+        <v>4952.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45634</v>
+        <v>17344</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pedro Miguel Caldeira</t>
+          <t>Benício da Cruz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -572,26 +572,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>45088</v>
       </c>
       <c r="G5" t="n">
-        <v>10203.73</v>
+        <v>6783.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82763</v>
+        <v>40261</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pedro Miguel Ramos</t>
+          <t>Benjamin Cunha</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -601,118 +601,118 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45086</v>
+        <v>45095</v>
       </c>
       <c r="G6" t="n">
-        <v>4654.88</v>
+        <v>6331.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45632</v>
+        <v>75895</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giovanna Cardoso</t>
+          <t>Milena Oliveira</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45091</v>
+        <v>45096</v>
       </c>
       <c r="G7" t="n">
-        <v>6890.95</v>
+        <v>4443.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>41738</v>
+        <v>58733</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Augusto Pinto</t>
+          <t>Pedro Miguel Campos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45086</v>
+        <v>45079</v>
       </c>
       <c r="G8" t="n">
-        <v>9390.82</v>
+        <v>8027.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48664</v>
+        <v>31446</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Beatriz Cardoso</t>
+          <t>Henrique Barros</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45098</v>
+        <v>45082</v>
       </c>
       <c r="G9" t="n">
-        <v>2842.81</v>
+        <v>9565.549999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15995</v>
+        <v>87006</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dra. Luiza Duarte</t>
+          <t>Marina Peixoto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,27 +721,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45091</v>
+        <v>45096</v>
       </c>
       <c r="G10" t="n">
-        <v>7202.74</v>
+        <v>3051.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11077</v>
+        <v>146</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sr. João Guilherme da Costa</t>
+          <t>Natália Costela</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45079</v>
+        <v>45085</v>
       </c>
       <c r="G11" t="n">
-        <v>7917.4</v>
+        <v>9388.549999999999</v>
       </c>
     </row>
   </sheetData>
